--- a/static/shared/vera-compliance/downloads/schema-riferimento.xlsx
+++ b/static/shared/vera-compliance/downloads/schema-riferimento.xlsx
@@ -17,7 +17,7 @@
     <sheet name="Fonti e verifiche" sheetId="7" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="3" name="_xlnm._FilterDatabase" vbProcedure="false">Funzionalità!$A$5:$J$35</definedName>
+    <definedName function="false" hidden="true" localSheetId="3" name="_xlnm._FilterDatabase" vbProcedure="false">Funzionalità!$A$5:$J$37</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -29,12 +29,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="419" uniqueCount="309">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="441" uniqueCount="326">
   <si>
     <t xml:space="preserve">Vera — Schema di ruoli, funzionalità e attività per la conformità GDPR / AI Act</t>
   </si>
   <si>
-    <t xml:space="preserve">Documento di lavoro da sottoporre agli sviluppatori — versione 0.1 del 03/10/2026</t>
+    <t xml:space="preserve">Documento di lavoro da sottoporre agli sviluppatori — versione 0.2 del 03/10/2026</t>
   </si>
   <si>
     <t xml:space="preserve">Finalità</t>
@@ -163,7 +163,7 @@
     <t xml:space="preserve">Da qualificare: sistema di IA (insieme al modello) oppure semplice orchestrazione</t>
   </si>
   <si>
-    <t xml:space="preserve">Condizioni per l'esenzione per software libero e open source (art. 2, par. 12, AI Act): non immesso come sistema ad alto rischio e non rientrante negli artt. 5 o 50. L'esenzione tutela il ruolo di provider, non gli obblighi del deployer.</t>
+    <t xml:space="preserve">Esenzione per i sistemi rilasciati con licenza libera e open source (art. 2, par. 12, AI Act): non opera se il sistema è immesso come sistema ad alto rischio o rientra negli artt. 5 o 50. Restano fermi il GDPR, la L. 132/2025 e l'applicazione del regolamento ai sistemi e ai modelli delle piattaforme sottostanti. Servizi collegati a pagamento o monetizzati, o uso di dati personali per scopi ulteriori, possono precludere i benefici dell'open source (considerando 103).</t>
   </si>
   <si>
     <t xml:space="preserve">Sviluppatori/comunità di Vera</t>
@@ -283,10 +283,10 @@
     <t xml:space="preserve">Funzioni che profilano persone fisiche (es. merito creditizio, lavoro, valutazione del rischio cliente)</t>
   </si>
   <si>
-    <t xml:space="preserve">Possibile rientro nei sistemi ad alto rischio (All. III): l'esenzione per software open source non opera; cambiano gli obblighi di provider e deployer.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Censimento delle skill rispetto all'All. III; verifica puntuale sul testo vigente; eventuale limitazione o avvisi d'uso.</t>
+    <t xml:space="preserve">Un sistema dell'All. III che effettua profilazione di persone fisiche è sempre ad alto rischio, senza deroga (art. 6, par. 3, terzo comma). L'esenzione open source non opera per i sistemi immessi come ad alto rischio. Gli obblighi del capo III per i sistemi dell'All. III si applicano dal 02/12/2027 (art. 113, come modificato dal Reg. UE 2026/1744).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Analisi funzione per funzione (tratta persone fisiche? produce valutazioni, punteggi o classificazioni?); per le funzioni ritenute non ad alto rischio, valutazione documentata e registrazione (art. 6, par. 4); eventuale limitazione o avvisi d'uso.</t>
   </si>
   <si>
     <t xml:space="preserve">Artt. 2 par. 12, 6 e All. III AI Act</t>
@@ -295,10 +295,10 @@
     <t xml:space="preserve">Funzioni soggette a obblighi di trasparenza (art. 50)</t>
   </si>
   <si>
-    <t xml:space="preserve">L'esenzione open source non opera per i sistemi che rientrano nell'art. 50. Gli obblighi di trasparenza del deployer sono applicabili dal 02/08/2026.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mappare se e dove Vera genera contenuti per terzi o interagisce con persone; disclosure standard sugli output.</t>
+    <t xml:space="preserve">L'esenzione open source non opera per i sistemi che rientrano nell'art. 50. Per i fornitori di sistemi che generano testo sintetico vale la marcatura leggibile dalle macchine (par. 2), con termine al 02/12/2026 per i sistemi già sul mercato prima del 02/08/2026 (art. 111, par. 4, Reg. UE 2026/1744); l'eccezione dell'editing standard è da dimostrare. Gli obblighi dei deployer (parr. 3-4) non riguardano le bozze professionali.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stabilire data di prima immissione sul mercato e soggetto che appone la marcatura (Vera o piattaforma); distinguere la marcatura tecnica dalla disclosure visibile dello studio (art. 13, co. 2, L. 132/2025).</t>
   </si>
   <si>
     <t xml:space="preserve">Art. 50 AI Act; art. 2 par. 12</t>
@@ -322,6 +322,18 @@
     <t xml:space="preserve">Matrice per provider con regime dichiarato e data di verifica; aggiornamento periodico.</t>
   </si>
   <si>
+    <t xml:space="preserve">Servizi collegati a pagamento o monetizzati; uso di dati personali per scopi ulteriori</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Possibile perdita dei benefici dell'esenzione open source (considerando 103); eventuale ruolo di titolare o responsabile di chi gestisce il servizio.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chiarire gratuità e finalità dei servizi collegati (compreso il servizio di ricevuta); indicare il soggetto che risponde dello sviluppo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Considerando 103 AI Act; artt. 4 n. 7-8, 28 GDPR</t>
+  </si>
+  <si>
     <t xml:space="preserve">Messaggi pubblici di conformità ("ci pensa Vera")</t>
   </si>
   <si>
@@ -508,7 +520,7 @@
     <t xml:space="preserve">G1.12</t>
   </si>
   <si>
-    <t xml:space="preserve">Censimento delle skill rispetto all'All. III AI Act e agli artt. 5 e 50, con indicazione di quelle che profilano persone fisiche</t>
+    <t xml:space="preserve">Analisi funzione per funzione rispetto all'All. III AI Act e all'art. 6, par. 3, con indicazione di quelle che trattano persone fisiche e producono valutazioni, punteggi o classificazioni</t>
   </si>
   <si>
     <t xml:space="preserve">Presidiare l'esenzione open source e il rischio di alto rischio</t>
@@ -529,6 +541,21 @@
     <t xml:space="preserve">Bassa</t>
   </si>
   <si>
+    <t xml:space="preserve">G1.14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marcatura leggibile dalle macchine dei testi generati e rilevabilità come generati artificialmente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rispettare l'obbligo dei fornitori di sistemi che generano testo sintetico</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Art. 50, par. 2 AI Act; art. 111, par. 4 (Reg. UE 2026/1744)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sviluppatori / Piattaforma</t>
+  </si>
+  <si>
     <t xml:space="preserve">D2.1</t>
   </si>
   <si>
@@ -724,6 +751,18 @@
     <t xml:space="preserve">Evitare obsolescenza non dichiarata</t>
   </si>
   <si>
+    <t xml:space="preserve">N3.8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dichiarazione del piano utilizzato all'avvio ed elenco dei presidi che Vera non copre, riportati anche nella documentazione d'uso</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Informare lo studio di ciò che resta a suo carico</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Artt. 4 n. 7, 24, 28 GDPR</t>
+  </si>
+  <si>
     <t xml:space="preserve">Domande agli sviluppatori</t>
   </si>
   <si>
@@ -826,6 +865,18 @@
     <t xml:space="preserve">Sicurezza e aggiornamento dei contenuti (art. 32 GDPR).</t>
   </si>
   <si>
+    <t xml:space="preserve">In che data è stata immessa sul mercato la prima versione di Vera? Chi appone oggi la marcatura leggibile dalle macchine dei testi generati (Vera o la piattaforma) e in quale formato?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Art. 50, par. 2 AI Act e termine transitorio dell'art. 111, par. 4 (Reg. UE 2026/1744).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I servizi collegati a Vera, compreso il servizio di ricevuta tecnica, sono gratuiti? Raccolgono dati personali per scopi ulteriori rispetto a sicurezza, compatibilità e interoperabilità?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Considerando 103 AI Act: servizi monetizzati o uso ulteriore di dati personali possono precludere i benefici dell'open source.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Riepilogo di avanzamento</t>
   </si>
   <si>
@@ -892,25 +943,25 @@
     <t xml:space="preserve">Ruoli provider/deployer, rischio, art. 4, art. 50, calendario</t>
   </si>
   <si>
-    <t xml:space="preserve">Schede di sintesi dello Studio verificate al 20/08/2026; versione consolidata EUR-Lex da riscontrare.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Act, art. 2, par. 12 (esenzione per sistemi di IA rilasciati con licenza libera e open source)</t>
+    <t xml:space="preserve">Artt. 1, nn. 5, 12, 39 e 40 letti sul testo ufficiale italiano (GU L del 24.7.2026, EUR-Lex).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Act, art. 2, par. 12 (esenzione per sistemi di IA rilasciati con licenza libera e open source) e considerando 102-103</t>
   </si>
   <si>
     <t xml:space="preserve">Qualificazione di Vera e condizioni dell'esenzione</t>
   </si>
   <si>
-    <t xml:space="preserve">Verificato su fonti secondarie (es. Linux Foundation Europe, explainer sull'AI Act); riscontrare sul testo ufficiale su EUR-Lex.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Act, All. III (sistemi ad alto rischio)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Censimento delle skill che profilano persone fisiche</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Da verificare sul testo dell'allegato (e sulle modifiche del Reg. UE 2026/1744) prima di qualsiasi conclusione.</t>
+    <t xml:space="preserve">Letto sul testo ufficiale italiano (GU L del 12.7.2024, EUR-Lex).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Act, art. 6, parr. 3-4; All. III, punto 5, lett. b); art. 50, par. 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Analisi di profilazione e marcatura dei testi generati</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Letti sul testo ufficiale italiano (GU L del 12.7.2024, EUR-Lex). Il Reg. UE 2026/1744 non modifica questi punti, salvo i termini transitori degli artt. 111 e 113.</t>
   </si>
   <si>
     <t xml:space="preserve">L. 132/2025, art. 13 (professioni intellettuali)</t>
@@ -919,7 +970,7 @@
     <t xml:space="preserve">Uso strumentale dell'IA e informativa al cliente</t>
   </si>
   <si>
-    <t xml:space="preserve">Da riscontrare su Normattiva (testo vigente).</t>
+    <t xml:space="preserve">Testo riscontrato su fonti secondarie; verifica su normattiva.it da completare.</t>
   </si>
   <si>
     <t xml:space="preserve">D.Lgs. 160/2026 (GU n. 214 del 15/09/2026, vigente dal 30/09/2026)</t>
@@ -1645,7 +1696,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="49.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="n">
         <v>4</v>
       </c>
@@ -1746,7 +1797,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A2:E14"/>
+  <dimension ref="A2:E15"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6"/>
@@ -1850,7 +1901,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="73.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="n">
         <v>5</v>
       </c>
@@ -1867,7 +1918,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="97" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="n">
         <v>6</v>
       </c>
@@ -1933,6 +1984,23 @@
       </c>
       <c r="E14" s="4" t="s">
         <v>100</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>104</v>
       </c>
     </row>
   </sheetData>
@@ -1951,7 +2019,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A2:J35"/>
+  <dimension ref="A2:J37"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8"/>
@@ -1968,67 +2036,67 @@
   <sheetData>
     <row r="2" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>2</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="H6" s="6"/>
       <c r="I6" s="6"/>
@@ -2036,25 +2104,25 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="E7" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="G7" s="4" t="s">
         <v>122</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>118</v>
       </c>
       <c r="H7" s="6"/>
       <c r="I7" s="6"/>
@@ -2062,25 +2130,25 @@
     </row>
     <row r="8" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="H8" s="6"/>
       <c r="I8" s="6"/>
@@ -2088,25 +2156,25 @@
     </row>
     <row r="9" customFormat="false" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="E9" s="4" t="s">
         <v>82</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="H9" s="6"/>
       <c r="I9" s="6"/>
@@ -2114,25 +2182,25 @@
     </row>
     <row r="10" customFormat="false" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="E10" s="4" t="s">
         <v>70</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="H10" s="6"/>
       <c r="I10" s="6"/>
@@ -2140,25 +2208,25 @@
     </row>
     <row r="11" customFormat="false" ht="49.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="E11" s="4" t="s">
         <v>74</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="H11" s="6"/>
       <c r="I11" s="6"/>
@@ -2166,25 +2234,25 @@
     </row>
     <row r="12" customFormat="false" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="E12" s="4" t="s">
         <v>78</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="H12" s="6"/>
       <c r="I12" s="6"/>
@@ -2192,25 +2260,25 @@
     </row>
     <row r="13" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="E13" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="G13" s="4" t="s">
         <v>144</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="G13" s="4" t="s">
-        <v>140</v>
       </c>
       <c r="H13" s="6"/>
       <c r="I13" s="6"/>
@@ -2218,25 +2286,25 @@
     </row>
     <row r="14" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="H14" s="6"/>
       <c r="I14" s="6"/>
@@ -2244,25 +2312,25 @@
     </row>
     <row r="15" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="H15" s="6"/>
       <c r="I15" s="6"/>
@@ -2270,51 +2338,51 @@
     </row>
     <row r="16" customFormat="false" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="H16" s="6"/>
       <c r="I16" s="6"/>
       <c r="J16" s="6"/>
     </row>
-    <row r="17" customFormat="false" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="49.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="H17" s="6"/>
       <c r="I17" s="6"/>
@@ -2322,25 +2390,25 @@
     </row>
     <row r="18" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="E18" s="4" t="s">
         <v>59</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="H18" s="6"/>
       <c r="I18" s="6"/>
@@ -2348,25 +2416,25 @@
     </row>
     <row r="19" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>167</v>
+        <v>117</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="H19" s="6"/>
       <c r="I19" s="6"/>
@@ -2374,77 +2442,77 @@
     </row>
     <row r="20" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="4" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>140</v>
+        <v>122</v>
       </c>
       <c r="H20" s="6"/>
       <c r="I20" s="6"/>
       <c r="J20" s="6"/>
     </row>
-    <row r="21" customFormat="false" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="B21" s="4" t="s">
         <v>176</v>
       </c>
-      <c r="B21" s="4" t="s">
-        <v>167</v>
-      </c>
       <c r="C21" s="4" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>118</v>
+        <v>144</v>
       </c>
       <c r="H21" s="6"/>
       <c r="I21" s="6"/>
       <c r="J21" s="6"/>
     </row>
-    <row r="22" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="F22" s="4" t="s">
         <v>180</v>
       </c>
-      <c r="B22" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>181</v>
-      </c>
-      <c r="D22" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="E22" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="F22" s="4" t="s">
-        <v>171</v>
-      </c>
       <c r="G22" s="4" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="H22" s="6"/>
       <c r="I22" s="6"/>
@@ -2452,259 +2520,259 @@
     </row>
     <row r="23" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="4" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>186</v>
+        <v>74</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>140</v>
+        <v>122</v>
       </c>
       <c r="H23" s="6"/>
       <c r="I23" s="6"/>
       <c r="J23" s="6"/>
     </row>
-    <row r="24" customFormat="false" ht="49.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="4" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="H24" s="6"/>
       <c r="I24" s="6"/>
       <c r="J24" s="6"/>
     </row>
-    <row r="25" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="49.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>165</v>
+        <v>144</v>
       </c>
       <c r="H25" s="6"/>
       <c r="I25" s="6"/>
       <c r="J25" s="6"/>
     </row>
-    <row r="26" customFormat="false" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="4" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>140</v>
+        <v>169</v>
       </c>
       <c r="H26" s="6"/>
       <c r="I26" s="6"/>
       <c r="J26" s="6"/>
     </row>
-    <row r="27" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="4" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="H27" s="6"/>
       <c r="I27" s="6"/>
       <c r="J27" s="6"/>
     </row>
-    <row r="28" customFormat="false" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="4" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>165</v>
+        <v>144</v>
       </c>
       <c r="H28" s="6"/>
       <c r="I28" s="6"/>
       <c r="J28" s="6"/>
     </row>
-    <row r="29" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="4" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>208</v>
+        <v>176</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>123</v>
+        <v>180</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>118</v>
+        <v>169</v>
       </c>
       <c r="H29" s="6"/>
       <c r="I29" s="6"/>
       <c r="J29" s="6"/>
     </row>
-    <row r="30" customFormat="false" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="4" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>74</v>
+        <v>220</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="H30" s="6"/>
       <c r="I30" s="6"/>
       <c r="J30" s="6"/>
     </row>
-    <row r="31" customFormat="false" ht="49.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="4" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="H31" s="6"/>
       <c r="I31" s="6"/>
       <c r="J31" s="6"/>
     </row>
-    <row r="32" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="49.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="4" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="H32" s="6"/>
       <c r="I32" s="6"/>
@@ -2712,90 +2780,142 @@
     </row>
     <row r="33" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="4" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="G33" s="4" t="s">
-        <v>140</v>
+        <v>122</v>
       </c>
       <c r="H33" s="6"/>
       <c r="I33" s="6"/>
       <c r="J33" s="6"/>
     </row>
-    <row r="34" customFormat="false" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="4" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>227</v>
+        <v>78</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>118</v>
+        <v>144</v>
       </c>
       <c r="H34" s="6"/>
       <c r="I34" s="6"/>
       <c r="J34" s="6"/>
     </row>
-    <row r="35" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="4" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>59</v>
+        <v>236</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="G35" s="4" t="s">
-        <v>140</v>
+        <v>122</v>
       </c>
       <c r="H35" s="6"/>
       <c r="I35" s="6"/>
       <c r="J35" s="6"/>
     </row>
+    <row r="36" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="D36" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="E36" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="F36" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="G36" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="H36" s="6"/>
+      <c r="I36" s="6"/>
+      <c r="J36" s="6"/>
+    </row>
+    <row r="37" customFormat="false" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="E37" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="F37" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="G37" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="H37" s="6"/>
+      <c r="I37" s="6"/>
+      <c r="J37" s="6"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A5:J35"/>
+  <autoFilter ref="A5:J37"/>
   <dataValidations count="2">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="H6:H35" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="H6:H37" type="list">
       <formula1>"Presente,Parziale,Assente,Non applicabile,Da valutare"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="G6:G35" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="G6:G37" type="list">
       <formula1>"Alta,Media,Bassa"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -2816,7 +2936,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A2:E19"/>
+  <dimension ref="A2:E21"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="7"/>
@@ -2828,12 +2948,12 @@
   <sheetData>
     <row r="2" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>231</v>
+        <v>244</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>232</v>
+        <v>245</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2841,16 +2961,16 @@
         <v>24</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>233</v>
+        <v>246</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>234</v>
+        <v>247</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>235</v>
+        <v>248</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>236</v>
+        <v>249</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2858,10 +2978,10 @@
         <v>1</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>237</v>
+        <v>250</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>238</v>
+        <v>251</v>
       </c>
       <c r="D6" s="6"/>
       <c r="E6" s="6"/>
@@ -2871,10 +2991,10 @@
         <v>2</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>239</v>
+        <v>252</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>240</v>
+        <v>253</v>
       </c>
       <c r="D7" s="6"/>
       <c r="E7" s="6"/>
@@ -2884,10 +3004,10 @@
         <v>3</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>241</v>
+        <v>254</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>242</v>
+        <v>255</v>
       </c>
       <c r="D8" s="6"/>
       <c r="E8" s="6"/>
@@ -2897,10 +3017,10 @@
         <v>4</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>243</v>
+        <v>256</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>244</v>
+        <v>257</v>
       </c>
       <c r="D9" s="6"/>
       <c r="E9" s="6"/>
@@ -2910,10 +3030,10 @@
         <v>5</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>246</v>
+        <v>259</v>
       </c>
       <c r="D10" s="6"/>
       <c r="E10" s="6"/>
@@ -2923,10 +3043,10 @@
         <v>6</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>247</v>
+        <v>260</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>248</v>
+        <v>261</v>
       </c>
       <c r="D11" s="6"/>
       <c r="E11" s="6"/>
@@ -2936,10 +3056,10 @@
         <v>7</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>249</v>
+        <v>262</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>250</v>
+        <v>263</v>
       </c>
       <c r="D12" s="6"/>
       <c r="E12" s="6"/>
@@ -2949,10 +3069,10 @@
         <v>8</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>251</v>
+        <v>264</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>252</v>
+        <v>265</v>
       </c>
       <c r="D13" s="6"/>
       <c r="E13" s="6"/>
@@ -2962,10 +3082,10 @@
         <v>9</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>253</v>
+        <v>266</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>254</v>
+        <v>267</v>
       </c>
       <c r="D14" s="6"/>
       <c r="E14" s="6"/>
@@ -2975,10 +3095,10 @@
         <v>10</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>255</v>
+        <v>268</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>256</v>
+        <v>269</v>
       </c>
       <c r="D15" s="6"/>
       <c r="E15" s="6"/>
@@ -2988,10 +3108,10 @@
         <v>11</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>257</v>
+        <v>270</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>258</v>
+        <v>271</v>
       </c>
       <c r="D16" s="6"/>
       <c r="E16" s="6"/>
@@ -3001,10 +3121,10 @@
         <v>12</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>259</v>
+        <v>272</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>260</v>
+        <v>273</v>
       </c>
       <c r="D17" s="6"/>
       <c r="E17" s="6"/>
@@ -3014,10 +3134,10 @@
         <v>13</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>261</v>
+        <v>274</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>262</v>
+        <v>275</v>
       </c>
       <c r="D18" s="6"/>
       <c r="E18" s="6"/>
@@ -3027,13 +3147,39 @@
         <v>14</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>263</v>
+        <v>276</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>264</v>
+        <v>277</v>
       </c>
       <c r="D19" s="6"/>
       <c r="E19" s="6"/>
+    </row>
+    <row r="20" customFormat="false" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>279</v>
+      </c>
+      <c r="D20" s="6"/>
+      <c r="E20" s="6"/>
+    </row>
+    <row r="21" customFormat="false" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>280</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="D21" s="6"/>
+      <c r="E21" s="6"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -3063,95 +3209,95 @@
   <sheetData>
     <row r="2" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>265</v>
+        <v>282</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>266</v>
+        <v>283</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>267</v>
+        <v>284</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>268</v>
+        <v>285</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>269</v>
+        <v>286</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>270</v>
+        <v>287</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>271</v>
+        <v>288</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>272</v>
+        <v>289</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>273</v>
+        <v>290</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="B6" s="8" t="n">
-        <f aca="false">COUNTIFS(Funzionalità!$B$6:$B$35,$A6,Funzionalità!$H$6:$H$35,"Presente")</f>
+        <f aca="false">COUNTIFS(Funzionalità!$B$6:$B$37,$A6,Funzionalità!$H$6:$H$37,"Presente")</f>
         <v>0</v>
       </c>
       <c r="C6" s="8" t="n">
-        <f aca="false">COUNTIFS(Funzionalità!$B$6:$B$35,$A6,Funzionalità!$H$6:$H$35,"Parziale")</f>
+        <f aca="false">COUNTIFS(Funzionalità!$B$6:$B$37,$A6,Funzionalità!$H$6:$H$37,"Parziale")</f>
         <v>0</v>
       </c>
       <c r="D6" s="8" t="n">
-        <f aca="false">COUNTIFS(Funzionalità!$B$6:$B$35,$A6,Funzionalità!$H$6:$H$35,"Assente")</f>
+        <f aca="false">COUNTIFS(Funzionalità!$B$6:$B$37,$A6,Funzionalità!$H$6:$H$37,"Assente")</f>
         <v>0</v>
       </c>
       <c r="E6" s="8" t="n">
-        <f aca="false">COUNTIFS(Funzionalità!$B$6:$B$35,$A6,Funzionalità!$H$6:$H$35,"Da valutare")</f>
+        <f aca="false">COUNTIFS(Funzionalità!$B$6:$B$37,$A6,Funzionalità!$H$6:$H$37,"Da valutare")</f>
         <v>0</v>
       </c>
       <c r="F6" s="8" t="n">
-        <f aca="false">COUNTIFS(Funzionalità!$B$6:$B$35,$A6,Funzionalità!$H$6:$H$35,"Non applicabile")</f>
+        <f aca="false">COUNTIFS(Funzionalità!$B$6:$B$37,$A6,Funzionalità!$H$6:$H$37,"Non applicabile")</f>
         <v>0</v>
       </c>
       <c r="G6" s="8" t="n">
         <f aca="false">H6-SUM(B6:F6)</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H6" s="8" t="n">
-        <f aca="false">COUNTIF(Funzionalità!$B$6:$B$35,$A6)</f>
-        <v>13</v>
+        <f aca="false">COUNTIF(Funzionalità!$B$6:$B$37,$A6)</f>
+        <v>14</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="B7" s="8" t="n">
-        <f aca="false">COUNTIFS(Funzionalità!$B$6:$B$35,$A7,Funzionalità!$H$6:$H$35,"Presente")</f>
+        <f aca="false">COUNTIFS(Funzionalità!$B$6:$B$37,$A7,Funzionalità!$H$6:$H$37,"Presente")</f>
         <v>0</v>
       </c>
       <c r="C7" s="8" t="n">
-        <f aca="false">COUNTIFS(Funzionalità!$B$6:$B$35,$A7,Funzionalità!$H$6:$H$35,"Parziale")</f>
+        <f aca="false">COUNTIFS(Funzionalità!$B$6:$B$37,$A7,Funzionalità!$H$6:$H$37,"Parziale")</f>
         <v>0</v>
       </c>
       <c r="D7" s="8" t="n">
-        <f aca="false">COUNTIFS(Funzionalità!$B$6:$B$35,$A7,Funzionalità!$H$6:$H$35,"Assente")</f>
+        <f aca="false">COUNTIFS(Funzionalità!$B$6:$B$37,$A7,Funzionalità!$H$6:$H$37,"Assente")</f>
         <v>0</v>
       </c>
       <c r="E7" s="8" t="n">
-        <f aca="false">COUNTIFS(Funzionalità!$B$6:$B$35,$A7,Funzionalità!$H$6:$H$35,"Da valutare")</f>
+        <f aca="false">COUNTIFS(Funzionalità!$B$6:$B$37,$A7,Funzionalità!$H$6:$H$37,"Da valutare")</f>
         <v>0</v>
       </c>
       <c r="F7" s="8" t="n">
-        <f aca="false">COUNTIFS(Funzionalità!$B$6:$B$35,$A7,Funzionalità!$H$6:$H$35,"Non applicabile")</f>
+        <f aca="false">COUNTIFS(Funzionalità!$B$6:$B$37,$A7,Funzionalità!$H$6:$H$37,"Non applicabile")</f>
         <v>0</v>
       </c>
       <c r="G7" s="8" t="n">
@@ -3159,46 +3305,46 @@
         <v>10</v>
       </c>
       <c r="H7" s="8" t="n">
-        <f aca="false">COUNTIF(Funzionalità!$B$6:$B$35,$A7)</f>
+        <f aca="false">COUNTIF(Funzionalità!$B$6:$B$37,$A7)</f>
         <v>10</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="B8" s="8" t="n">
-        <f aca="false">COUNTIFS(Funzionalità!$B$6:$B$35,$A8,Funzionalità!$H$6:$H$35,"Presente")</f>
+        <f aca="false">COUNTIFS(Funzionalità!$B$6:$B$37,$A8,Funzionalità!$H$6:$H$37,"Presente")</f>
         <v>0</v>
       </c>
       <c r="C8" s="8" t="n">
-        <f aca="false">COUNTIFS(Funzionalità!$B$6:$B$35,$A8,Funzionalità!$H$6:$H$35,"Parziale")</f>
+        <f aca="false">COUNTIFS(Funzionalità!$B$6:$B$37,$A8,Funzionalità!$H$6:$H$37,"Parziale")</f>
         <v>0</v>
       </c>
       <c r="D8" s="8" t="n">
-        <f aca="false">COUNTIFS(Funzionalità!$B$6:$B$35,$A8,Funzionalità!$H$6:$H$35,"Assente")</f>
+        <f aca="false">COUNTIFS(Funzionalità!$B$6:$B$37,$A8,Funzionalità!$H$6:$H$37,"Assente")</f>
         <v>0</v>
       </c>
       <c r="E8" s="8" t="n">
-        <f aca="false">COUNTIFS(Funzionalità!$B$6:$B$35,$A8,Funzionalità!$H$6:$H$35,"Da valutare")</f>
+        <f aca="false">COUNTIFS(Funzionalità!$B$6:$B$37,$A8,Funzionalità!$H$6:$H$37,"Da valutare")</f>
         <v>0</v>
       </c>
       <c r="F8" s="8" t="n">
-        <f aca="false">COUNTIFS(Funzionalità!$B$6:$B$35,$A8,Funzionalità!$H$6:$H$35,"Non applicabile")</f>
+        <f aca="false">COUNTIFS(Funzionalità!$B$6:$B$37,$A8,Funzionalità!$H$6:$H$37,"Non applicabile")</f>
         <v>0</v>
       </c>
       <c r="G8" s="8" t="n">
         <f aca="false">H8-SUM(B8:F8)</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H8" s="8" t="n">
-        <f aca="false">COUNTIF(Funzionalità!$B$6:$B$35,$A8)</f>
-        <v>7</v>
+        <f aca="false">COUNTIF(Funzionalità!$B$6:$B$37,$A8)</f>
+        <v>8</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="9" t="s">
-        <v>273</v>
+        <v>290</v>
       </c>
       <c r="B9" s="10" t="n">
         <f aca="false">SUM(B6:B8)</f>
@@ -3222,24 +3368,24 @@
       </c>
       <c r="G9" s="10" t="n">
         <f aca="false">SUM(G6:G8)</f>
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H9" s="10" t="n">
         <f aca="false">SUM(H6:H8)</f>
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="11" t="s">
-        <v>274</v>
+        <v>291</v>
       </c>
       <c r="B11" s="12" t="n">
-        <f aca="false">COUNTA('Domande agli sviluppatori'!D6:D19)</f>
+        <f aca="false">COUNTA('Domande agli sviluppatori'!D6:D21)</f>
         <v>0</v>
       </c>
       <c r="C11" s="12" t="str">
-        <f aca="false">"su "&amp;COUNTA('Domande agli sviluppatori'!A6:A19)</f>
-        <v>su 14</v>
+        <f aca="false">"su "&amp;COUNTA('Domande agli sviluppatori'!A6:A21)</f>
+        <v>su 16</v>
       </c>
     </row>
   </sheetData>
@@ -3270,12 +3416,12 @@
   <sheetData>
     <row r="2" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>275</v>
+        <v>292</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>276</v>
+        <v>293</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3283,16 +3429,16 @@
         <v>24</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>277</v>
+        <v>294</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>278</v>
+        <v>295</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>279</v>
+        <v>296</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>280</v>
+        <v>297</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3300,16 +3446,16 @@
         <v>1</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>281</v>
+        <v>298</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>283</v>
+        <v>300</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>284</v>
+        <v>301</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3317,16 +3463,16 @@
         <v>2</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>285</v>
+        <v>302</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>286</v>
+        <v>303</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>283</v>
+        <v>300</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>287</v>
+        <v>304</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3334,50 +3480,50 @@
         <v>3</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>288</v>
+        <v>305</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>289</v>
+        <v>306</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>283</v>
+        <v>300</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="n">
         <v>4</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>291</v>
+        <v>308</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>292</v>
+        <v>309</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>59</v>
+        <v>300</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="n">
         <v>5</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>294</v>
+        <v>311</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>295</v>
+        <v>312</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>283</v>
+        <v>300</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>296</v>
+        <v>313</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3385,16 +3531,16 @@
         <v>6</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>297</v>
+        <v>314</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>298</v>
+        <v>315</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>283</v>
+        <v>300</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>299</v>
+        <v>316</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3402,16 +3548,16 @@
         <v>7</v>
       </c>
       <c r="B12" s="4" t="s">
+        <v>317</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>318</v>
+      </c>
+      <c r="D12" s="4" t="s">
         <v>300</v>
       </c>
-      <c r="C12" s="4" t="s">
-        <v>301</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>283</v>
-      </c>
       <c r="E12" s="4" t="s">
-        <v>302</v>
+        <v>319</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3419,16 +3565,16 @@
         <v>8</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>303</v>
+        <v>320</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>304</v>
+        <v>321</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>283</v>
+        <v>300</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>305</v>
+        <v>322</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3436,16 +3582,16 @@
         <v>9</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>306</v>
+        <v>323</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>307</v>
+        <v>324</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>59</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>308</v>
+        <v>325</v>
       </c>
     </row>
   </sheetData>
